--- a/examples/report.xlsx
+++ b/examples/report.xlsx
@@ -621,7 +621,7 @@
         <v>0.53</v>
       </c>
       <c r="L2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -653,13 +653,13 @@
         <v>0.315</v>
       </c>
       <c r="J3">
-        <v>0.338</v>
+        <v>0.3395</v>
       </c>
       <c r="K3">
         <v>0.35</v>
       </c>
       <c r="L3">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:13">

--- a/examples/report.xlsx
+++ b/examples/report.xlsx
@@ -15,7 +15,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
+  <si>
+    <t>Host</t>
+  </si>
   <si>
     <t>Start</t>
   </si>
@@ -56,6 +59,9 @@
     <t>In quiet hours</t>
   </si>
   <si>
+    <t>ce2</t>
+  </si>
+  <si>
     <t>2026-10-18T19:30:00+02:00</t>
   </si>
   <si>
@@ -146,10 +152,7 @@
     <t>bluez_output.F8_4E_17_02_9A_C1.1</t>
   </si>
   <si>
-    <t>Host</t>
-  </si>
-  <si>
-    <t>ce2</t>
+    <t>Hosts</t>
   </si>
   <si>
     <t>Window</t>
@@ -170,16 +173,16 @@
     <t>intact (118 lines)</t>
   </si>
   <si>
-    <t>2026-10-18</t>
+    <t>ce2 2026-10-18</t>
   </si>
   <si>
     <t>dfn not yet stamped, digicert not yet stamped</t>
   </si>
   <si>
-    <t>2026-10-19</t>
-  </si>
-  <si>
-    <t>2026-10-20</t>
+    <t>ce2 2026-10-19</t>
+  </si>
+  <si>
+    <t>ce2 2026-10-20</t>
   </si>
 </sst>
 </file>
@@ -529,23 +532,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="40.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="46.7109375" customWidth="1"/>
-    <col min="8" max="8" width="40.7109375" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="3" width="24.7109375" customWidth="1"/>
+    <col min="4" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="40.7109375" customWidth="1"/>
+    <col min="7" max="7" width="22.7109375" customWidth="1"/>
+    <col min="8" max="8" width="46.7109375" customWidth="1"/>
+    <col min="9" max="9" width="40.7109375" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -585,159 +589,174 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2">
+        <v>0.47</v>
+      </c>
+      <c r="K2">
+        <v>0.5</v>
+      </c>
+      <c r="L2">
+        <v>0.53</v>
+      </c>
+      <c r="M2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3">
+        <v>0.315</v>
+      </c>
+      <c r="K3">
+        <v>0.3395</v>
+      </c>
+      <c r="L3">
+        <v>0.35</v>
+      </c>
+      <c r="M3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
         <v>18</v>
       </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2">
-        <v>0.47</v>
-      </c>
-      <c r="J2">
-        <v>0.5</v>
-      </c>
-      <c r="K2">
-        <v>0.53</v>
-      </c>
-      <c r="L2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3">
-        <v>0.315</v>
-      </c>
-      <c r="J3">
-        <v>0.3395</v>
-      </c>
-      <c r="K3">
-        <v>0.35</v>
-      </c>
-      <c r="L3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="J4">
+        <v>0.42</v>
+      </c>
+      <c r="K4">
+        <v>0.5455000000000001</v>
+      </c>
+      <c r="L4">
+        <v>0.68</v>
+      </c>
+      <c r="M4">
         <v>32</v>
       </c>
-      <c r="G4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4">
-        <v>0.42</v>
-      </c>
-      <c r="J4">
-        <v>0.5455000000000001</v>
-      </c>
-      <c r="K4">
-        <v>0.68</v>
-      </c>
-      <c r="L4">
-        <v>32</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5">
+        <v>43</v>
+      </c>
+      <c r="I5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5">
         <v>0.36</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>0.3775</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>0.4</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>10</v>
       </c>
     </row>
@@ -757,58 +776,58 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s">
         <v>53</v>
-      </c>
-      <c r="B6" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/examples/report.xlsx
+++ b/examples/report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
   <si>
     <t>Host</t>
   </si>
@@ -65,10 +65,10 @@
     <t>2026-10-18T19:30:00+02:00</t>
   </si>
   <si>
-    <t>2026-10-18T21:50:00+02:00</t>
-  </si>
-  <si>
-    <t>2h20m</t>
+    <t>2026-10-18T21:25:00+02:00</t>
+  </si>
+  <si>
+    <t>1h55m</t>
   </si>
   <si>
     <t>mpd</t>
@@ -86,70 +86,13 @@
     <t>alsa_output.usb-Focusrite_Scarlett_4i4_USB-00.pro-output-0</t>
   </si>
   <si>
-    <t>2026-10-19T15:00:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-19T17:10:00+02:00</t>
-  </si>
-  <si>
-    <t>2h10m</t>
-  </si>
-  <si>
-    <t>mpv</t>
-  </si>
-  <si>
-    <t>Stalker (1979)</t>
-  </si>
-  <si>
-    <t>Andrei Tarkovsky</t>
-  </si>
-  <si>
-    <t>/media/films/stalker.mkv</t>
-  </si>
-  <si>
-    <t>2026-10-19T21:10:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-19T23:40:00+02:00</t>
-  </si>
-  <si>
-    <t>2h30m</t>
-  </si>
-  <si>
-    <t>II (Continuous Mix)</t>
-  </si>
-  <si>
-    <t>Voices from the Lake</t>
-  </si>
-  <si>
-    <t>sync/vftl/11.flac</t>
-  </si>
-  <si>
-    <t>1h40m</t>
-  </si>
-  <si>
-    <t>2026-10-20T20:00:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-20T20:40:00+02:00</t>
-  </si>
-  <si>
-    <t>40m00s</t>
-  </si>
-  <si>
-    <t>firefox</t>
-  </si>
-  <si>
-    <t>Nils Frahm — Says (Live)</t>
-  </si>
-  <si>
-    <t>Nils Frahm</t>
-  </si>
-  <si>
-    <t>https://youtube.com/watch?v=dIww</t>
-  </si>
-  <si>
-    <t>bluez_output.F8_4E_17_02_9A_C1.1</t>
+    <t>2026-10-19T19:30:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T21:30:00+02:00</t>
+  </si>
+  <si>
+    <t>2h00m</t>
   </si>
   <si>
     <t>Hosts</t>
@@ -170,7 +113,7 @@
     <t>Chain</t>
   </si>
   <si>
-    <t>intact (118 lines)</t>
+    <t>intact (2756 lines)</t>
   </si>
   <si>
     <t>ce2 2026-10-18</t>
@@ -182,14 +125,14 @@
     <t>ce2 2026-10-19</t>
   </si>
   <si>
-    <t>ce2 2026-10-20</t>
+    <t>ce2 2026-10-21</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,14 +144,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFB03030"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -234,10 +169,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -532,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -622,16 +556,16 @@
         <v>22</v>
       </c>
       <c r="J2">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="K2">
-        <v>0.5</v>
+        <v>0.448</v>
       </c>
       <c r="L2">
-        <v>0.53</v>
+        <v>0.48</v>
       </c>
       <c r="M2">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -648,116 +582,31 @@
         <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
       </c>
       <c r="J3">
-        <v>0.315</v>
+        <v>0.4</v>
       </c>
       <c r="K3">
-        <v>0.3395</v>
+        <v>0.4485</v>
       </c>
       <c r="L3">
-        <v>0.35</v>
+        <v>0.48</v>
       </c>
       <c r="M3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4">
-        <v>0.42</v>
-      </c>
-      <c r="K4">
-        <v>0.5455000000000001</v>
-      </c>
-      <c r="L4">
-        <v>0.68</v>
-      </c>
-      <c r="M4">
-        <v>32</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5">
-        <v>0.36</v>
-      </c>
-      <c r="K5">
-        <v>0.3775</v>
-      </c>
-      <c r="L5">
-        <v>0.4</v>
-      </c>
-      <c r="M5">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -776,7 +625,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
         <v>14</v>
@@ -784,50 +633,50 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/examples/report.xlsx
+++ b/examples/report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
   <si>
     <t>Host</t>
   </si>
@@ -62,37 +62,70 @@
     <t>ce2</t>
   </si>
   <si>
-    <t>2026-10-18T19:30:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-18T21:25:00+02:00</t>
-  </si>
-  <si>
-    <t>1h55m</t>
+    <t>2026-10-18T18:00:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-18T20:30:00+02:00</t>
+  </si>
+  <si>
+    <t>2h30m</t>
   </si>
   <si>
     <t>mpd</t>
   </si>
   <si>
-    <t>Music for 18 Musicians</t>
-  </si>
-  <si>
-    <t>Steve Reich</t>
-  </si>
-  <si>
-    <t>sync/reich/01.flac</t>
+    <t>Harmony of Difference</t>
+  </si>
+  <si>
+    <t>Kamasi Washington</t>
+  </si>
+  <si>
+    <t>sync/kamasi/truth.flac</t>
   </si>
   <si>
     <t>alsa_output.usb-Focusrite_Scarlett_4i4_USB-00.pro-output-0</t>
   </si>
   <si>
-    <t>2026-10-19T19:30:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-19T21:30:00+02:00</t>
-  </si>
-  <si>
-    <t>2h00m</t>
+    <t>2026-10-18T21:10:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-18T22:40:00+02:00</t>
+  </si>
+  <si>
+    <t>1h30m</t>
+  </si>
+  <si>
+    <t>II (Continuous Mix)</t>
+  </si>
+  <si>
+    <t>Voices from the Lake</t>
+  </si>
+  <si>
+    <t>sync/vftl/11.flac</t>
+  </si>
+  <si>
+    <t>40m00s</t>
+  </si>
+  <si>
+    <t>2026-10-19T21:15:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T23:05:00+02:00</t>
+  </si>
+  <si>
+    <t>1h50m</t>
+  </si>
+  <si>
+    <t>Discreet Music</t>
+  </si>
+  <si>
+    <t>Brian Eno</t>
+  </si>
+  <si>
+    <t>sync/eno/discreet.flac</t>
+  </si>
+  <si>
+    <t>1h05m</t>
   </si>
   <si>
     <t>Hosts</t>
@@ -113,7 +146,7 @@
     <t>Chain</t>
   </si>
   <si>
-    <t>intact (2756 lines)</t>
+    <t>intact (2932 lines)</t>
   </si>
   <si>
     <t>ce2 2026-10-18</t>
@@ -132,7 +165,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,6 +177,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFB03030"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -169,9 +210,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -466,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -556,16 +598,16 @@
         <v>22</v>
       </c>
       <c r="J2">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="K2">
-        <v>0.448</v>
+        <v>0.477</v>
       </c>
       <c r="L2">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="M2">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -585,28 +627,75 @@
         <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
       </c>
       <c r="J3">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="K3">
-        <v>0.4485</v>
+        <v>0.4935</v>
       </c>
       <c r="L3">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="M3">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4">
+        <v>0.34</v>
+      </c>
+      <c r="K4">
+        <v>0.3895</v>
+      </c>
+      <c r="L4">
+        <v>0.42</v>
+      </c>
+      <c r="M4">
+        <v>24</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +714,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
         <v>14</v>
@@ -633,50 +722,50 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/examples/report.xlsx
+++ b/examples/report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="72">
   <si>
     <t>Host</t>
   </si>
@@ -59,19 +59,64 @@
     <t>In quiet hours</t>
   </si>
   <si>
+    <t>ce3</t>
+  </si>
+  <si>
+    <t>2026-10-18T09:40:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-18T11:30:00+02:00</t>
+  </si>
+  <si>
+    <t>1h50m</t>
+  </si>
+  <si>
+    <t>firefox</t>
+  </si>
+  <si>
+    <t>Nils Frahm — Says (Live)</t>
+  </si>
+  <si>
+    <t>Nils Frahm</t>
+  </si>
+  <si>
+    <t>https://youtube.com/watch?v=dIww</t>
+  </si>
+  <si>
+    <t>alsa_output.pci-0000_00_1f.3.analog-stereo</t>
+  </si>
+  <si>
+    <t>2026-10-18T13:40:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-18T15:10:00+02:00</t>
+  </si>
+  <si>
+    <t>1h30m</t>
+  </si>
+  <si>
+    <t>mpd</t>
+  </si>
+  <si>
+    <t>Spiegel im Spiegel</t>
+  </si>
+  <si>
+    <t>Arvo Pärt</t>
+  </si>
+  <si>
+    <t>sync/part/spiegel.flac</t>
+  </si>
+  <si>
     <t>ce2</t>
   </si>
   <si>
-    <t>2026-10-18T18:00:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-18T20:30:00+02:00</t>
-  </si>
-  <si>
-    <t>2h30m</t>
-  </si>
-  <si>
-    <t>mpd</t>
+    <t>2026-10-18T21:00:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-18T23:40:00+02:00</t>
+  </si>
+  <si>
+    <t>2h40m</t>
   </si>
   <si>
     <t>Harmony of Difference</t>
@@ -86,25 +131,7 @@
     <t>alsa_output.usb-Focusrite_Scarlett_4i4_USB-00.pro-output-0</t>
   </si>
   <si>
-    <t>2026-10-18T21:10:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-18T22:40:00+02:00</t>
-  </si>
-  <si>
-    <t>1h30m</t>
-  </si>
-  <si>
-    <t>II (Continuous Mix)</t>
-  </si>
-  <si>
-    <t>Voices from the Lake</t>
-  </si>
-  <si>
-    <t>sync/vftl/11.flac</t>
-  </si>
-  <si>
-    <t>40m00s</t>
+    <t>1h40m</t>
   </si>
   <si>
     <t>2026-10-19T21:15:00+02:00</t>
@@ -113,9 +140,6 @@
     <t>2026-10-19T23:05:00+02:00</t>
   </si>
   <si>
-    <t>1h50m</t>
-  </si>
-  <si>
     <t>Discreet Music</t>
   </si>
   <si>
@@ -128,9 +152,48 @@
     <t>1h05m</t>
   </si>
   <si>
+    <t>2026-10-20T14:00:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-20T16:40:00+02:00</t>
+  </si>
+  <si>
+    <t>mpv</t>
+  </si>
+  <si>
+    <t>Stalker (1979)</t>
+  </si>
+  <si>
+    <t>Andrei Tarkovsky</t>
+  </si>
+  <si>
+    <t>/media/films/stalker.mkv</t>
+  </si>
+  <si>
+    <t>2026-10-20T20:30:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-20T21:50:00+02:00</t>
+  </si>
+  <si>
+    <t>1h20m</t>
+  </si>
+  <si>
+    <t>A Rainbow in Curved Air</t>
+  </si>
+  <si>
+    <t>Terry Riley</t>
+  </si>
+  <si>
+    <t>sync/riley/rainbow.flac</t>
+  </si>
+  <si>
     <t>Hosts</t>
   </si>
   <si>
+    <t>ce2, ce3</t>
+  </si>
+  <si>
     <t>Window</t>
   </si>
   <si>
@@ -146,7 +209,7 @@
     <t>Chain</t>
   </si>
   <si>
-    <t>intact (2932 lines)</t>
+    <t>intact (6099 lines)</t>
   </si>
   <si>
     <t>ce2 2026-10-18</t>
@@ -155,10 +218,19 @@
     <t>dfn not yet stamped, digicert not yet stamped</t>
   </si>
   <si>
+    <t>ce3 2026-10-18</t>
+  </si>
+  <si>
     <t>ce2 2026-10-19</t>
   </si>
   <si>
+    <t>ce2 2026-10-20</t>
+  </si>
+  <si>
     <t>ce2 2026-10-21</t>
+  </si>
+  <si>
+    <t>ce3 2026-10-21</t>
   </si>
 </sst>
 </file>
@@ -508,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -598,16 +670,16 @@
         <v>22</v>
       </c>
       <c r="J2">
-        <v>0.44</v>
+        <v>0.197</v>
       </c>
       <c r="K2">
-        <v>0.477</v>
+        <v>0.23399999999999999</v>
       </c>
       <c r="L2">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="M2">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -624,78 +696,201 @@
         <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
       </c>
       <c r="J3">
-        <v>0.47</v>
+        <v>0.25</v>
       </c>
       <c r="K3">
-        <v>0.4935</v>
+        <v>0.2595</v>
       </c>
       <c r="L3">
-        <v>0.52</v>
+        <v>0.27</v>
       </c>
       <c r="M3">
         <v>20</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4">
+        <v>0.42</v>
+      </c>
+      <c r="K4">
+        <v>0.546</v>
+      </c>
+      <c r="L4">
+        <v>0.68</v>
+      </c>
+      <c r="M4">
+        <v>34</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
         <v>30</v>
       </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5">
+        <v>0.34</v>
+      </c>
+      <c r="K5">
+        <v>0.3895</v>
+      </c>
+      <c r="L5">
+        <v>0.42</v>
+      </c>
+      <c r="M5">
+        <v>24</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6">
+        <v>0.315</v>
+      </c>
+      <c r="K6">
+        <v>0.34</v>
+      </c>
+      <c r="L6">
+        <v>0.35</v>
+      </c>
+      <c r="M6">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7">
+        <v>0.41</v>
+      </c>
+      <c r="K7">
+        <v>0.44</v>
+      </c>
+      <c r="L7">
+        <v>0.47</v>
+      </c>
+      <c r="M7">
         <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4">
-        <v>0.34</v>
-      </c>
-      <c r="K4">
-        <v>0.3895</v>
-      </c>
-      <c r="L4">
-        <v>0.42</v>
-      </c>
-      <c r="M4">
-        <v>24</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +900,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
@@ -714,58 +909,82 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/examples/report.xlsx
+++ b/examples/report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="60">
   <si>
     <t>Host</t>
   </si>
@@ -59,64 +59,55 @@
     <t>In quiet hours</t>
   </si>
   <si>
-    <t>ce3</t>
-  </si>
-  <si>
-    <t>2026-10-18T09:40:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-18T11:30:00+02:00</t>
-  </si>
-  <si>
-    <t>1h50m</t>
-  </si>
-  <si>
-    <t>firefox</t>
-  </si>
-  <si>
-    <t>Nils Frahm — Says (Live)</t>
-  </si>
-  <si>
-    <t>Nils Frahm</t>
-  </si>
-  <si>
-    <t>https://youtube.com/watch?v=dIww</t>
-  </si>
-  <si>
-    <t>alsa_output.pci-0000_00_1f.3.analog-stereo</t>
-  </si>
-  <si>
-    <t>2026-10-18T13:40:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-18T15:10:00+02:00</t>
-  </si>
-  <si>
-    <t>1h30m</t>
+    <t>ce2</t>
+  </si>
+  <si>
+    <t>2026-10-18T20:30:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-18T21:40:00+02:00</t>
+  </si>
+  <si>
+    <t>1h10m</t>
   </si>
   <si>
     <t>mpd</t>
   </si>
   <si>
-    <t>Spiegel im Spiegel</t>
-  </si>
-  <si>
-    <t>Arvo Pärt</t>
-  </si>
-  <si>
-    <t>sync/part/spiegel.flac</t>
-  </si>
-  <si>
-    <t>ce2</t>
-  </si>
-  <si>
-    <t>2026-10-18T21:00:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-18T23:40:00+02:00</t>
-  </si>
-  <si>
-    <t>2h40m</t>
+    <t>Selected Ambient Works Volume II</t>
+  </si>
+  <si>
+    <t>Aphex Twin</t>
+  </si>
+  <si>
+    <t>sync/afx/saw2-03.flac</t>
+  </si>
+  <si>
+    <t>alsa_output.usb-Focusrite_Scarlett_4i4_USB-00.pro-output-0</t>
+  </si>
+  <si>
+    <t>2026-10-18T22:00:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-18T23:10:00+02:00</t>
+  </si>
+  <si>
+    <t>The Disintegration Loops I</t>
+  </si>
+  <si>
+    <t>William Basinski</t>
+  </si>
+  <si>
+    <t>sync/basinski/dlp1.flac</t>
+  </si>
+  <si>
+    <t>2026-10-18T23:37:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-18T23:47:00+02:00</t>
+  </si>
+  <si>
+    <t>10m00s</t>
   </si>
   <si>
     <t>Harmony of Difference</t>
@@ -128,16 +119,13 @@
     <t>sync/kamasi/truth.flac</t>
   </si>
   <si>
-    <t>alsa_output.usb-Focusrite_Scarlett_4i4_USB-00.pro-output-0</t>
-  </si>
-  <si>
-    <t>1h40m</t>
-  </si>
-  <si>
-    <t>2026-10-19T21:15:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-19T23:05:00+02:00</t>
+    <t>2026-10-19T21:25:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T23:35:00+02:00</t>
+  </si>
+  <si>
+    <t>2h10m</t>
   </si>
   <si>
     <t>Discreet Music</t>
@@ -149,43 +137,25 @@
     <t>sync/eno/discreet.flac</t>
   </si>
   <si>
-    <t>1h05m</t>
-  </si>
-  <si>
-    <t>2026-10-20T14:00:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-20T16:40:00+02:00</t>
-  </si>
-  <si>
-    <t>mpv</t>
-  </si>
-  <si>
-    <t>Stalker (1979)</t>
-  </si>
-  <si>
-    <t>Andrei Tarkovsky</t>
-  </si>
-  <si>
-    <t>/media/films/stalker.mkv</t>
-  </si>
-  <si>
-    <t>2026-10-20T20:30:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-20T21:50:00+02:00</t>
-  </si>
-  <si>
-    <t>1h20m</t>
-  </si>
-  <si>
-    <t>A Rainbow in Curved Air</t>
-  </si>
-  <si>
-    <t>Terry Riley</t>
-  </si>
-  <si>
-    <t>sync/riley/rainbow.flac</t>
+    <t>1h35m</t>
+  </si>
+  <si>
+    <t>2026-10-20T22:30:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-20T23:30:00+02:00</t>
+  </si>
+  <si>
+    <t>1h00m</t>
+  </si>
+  <si>
+    <t>Symphony No. 3, Op. 36: II. Lento</t>
+  </si>
+  <si>
+    <t>Henryk Górecki</t>
+  </si>
+  <si>
+    <t>sync/gorecki/02.flac</t>
   </si>
   <si>
     <t>Hosts</t>
@@ -209,7 +179,7 @@
     <t>Chain</t>
   </si>
   <si>
-    <t>intact (6099 lines)</t>
+    <t>intact (5069 lines)</t>
   </si>
   <si>
     <t>ce2 2026-10-18</t>
@@ -218,16 +188,10 @@
     <t>dfn not yet stamped, digicert not yet stamped</t>
   </si>
   <si>
-    <t>ce3 2026-10-18</t>
-  </si>
-  <si>
     <t>ce2 2026-10-19</t>
   </si>
   <si>
     <t>ce2 2026-10-20</t>
-  </si>
-  <si>
-    <t>ce2 2026-10-21</t>
   </si>
   <si>
     <t>ce3 2026-10-21</t>
@@ -580,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -670,16 +634,16 @@
         <v>22</v>
       </c>
       <c r="J2">
-        <v>0.197</v>
+        <v>0.37</v>
       </c>
       <c r="K2">
-        <v>0.23399999999999999</v>
+        <v>0.405</v>
       </c>
       <c r="L2">
-        <v>0.25</v>
+        <v>0.43</v>
       </c>
       <c r="M2">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -693,204 +657,169 @@
         <v>24</v>
       </c>
       <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
         <v>25</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>26</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>27</v>
-      </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" t="s">
-        <v>29</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
       </c>
       <c r="J3">
-        <v>0.25</v>
+        <v>0.39</v>
       </c>
       <c r="K3">
-        <v>0.2595</v>
+        <v>0.426</v>
       </c>
       <c r="L3">
-        <v>0.27</v>
+        <v>0.45</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
         <v>31</v>
       </c>
-      <c r="C4" t="s">
+      <c r="G4" t="s">
         <v>32</v>
       </c>
-      <c r="D4" t="s">
+      <c r="H4" t="s">
         <v>33</v>
       </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" t="s">
-        <v>36</v>
-      </c>
       <c r="I4" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="J4">
-        <v>0.42</v>
+        <v>0.421</v>
       </c>
       <c r="K4">
-        <v>0.546</v>
+        <v>0.44</v>
       </c>
       <c r="L4">
-        <v>0.68</v>
+        <v>0.468</v>
       </c>
       <c r="M4">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" t="s">
         <v>39</v>
       </c>
-      <c r="C5" t="s">
+      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5">
+        <v>0.42</v>
+      </c>
+      <c r="K5">
+        <v>0.5045</v>
+      </c>
+      <c r="L5">
+        <v>0.596</v>
+      </c>
+      <c r="M5">
+        <v>28</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5">
-        <v>0.34</v>
-      </c>
-      <c r="K5">
-        <v>0.3895</v>
-      </c>
-      <c r="L5">
-        <v>0.42</v>
-      </c>
-      <c r="M5">
-        <v>24</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" t="s">
         <v>45</v>
       </c>
-      <c r="C6" t="s">
+      <c r="H6" t="s">
         <v>46</v>
       </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" t="s">
-        <v>50</v>
-      </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="J6">
-        <v>0.315</v>
+        <v>0.35</v>
       </c>
       <c r="K6">
-        <v>0.34</v>
+        <v>0.3945</v>
       </c>
       <c r="L6">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="M6">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7">
-        <v>0.41</v>
-      </c>
-      <c r="K7">
-        <v>0.44</v>
-      </c>
-      <c r="L7">
-        <v>0.47</v>
-      </c>
-      <c r="M7">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -900,7 +829,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
@@ -909,82 +838,66 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/examples/report.xlsx
+++ b/examples/report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="58">
   <si>
     <t>Host</t>
   </si>
@@ -182,16 +182,10 @@
     <t>intact (5069 lines)</t>
   </si>
   <si>
-    <t>ce2 2026-10-18</t>
+    <t>ce2 2026-10-18 … 2026-10-20  (3 days)</t>
   </si>
   <si>
     <t>dfn not yet stamped, digicert not yet stamped</t>
-  </si>
-  <si>
-    <t>ce2 2026-10-19</t>
-  </si>
-  <si>
-    <t>ce2 2026-10-20</t>
   </si>
   <si>
     <t>ce3 2026-10-21</t>
@@ -829,7 +823,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
@@ -884,22 +878,6 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" t="s">
-        <v>56</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/examples/report.xlsx
+++ b/examples/report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="61">
   <si>
     <t>Host</t>
   </si>
@@ -62,72 +62,60 @@
     <t>ce2</t>
   </si>
   <si>
-    <t>2026-10-18T20:30:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-18T21:40:00+02:00</t>
+    <t>2026-10-18T14:40:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-18T16:40:00+02:00</t>
+  </si>
+  <si>
+    <t>2h00m</t>
+  </si>
+  <si>
+    <t>mpv</t>
+  </si>
+  <si>
+    <t>Sans Soleil (1983)</t>
+  </si>
+  <si>
+    <t>Chris Marker</t>
+  </si>
+  <si>
+    <t>/media/films/sans-soleil.mkv</t>
+  </si>
+  <si>
+    <t>alsa_output.usb-Focusrite_Scarlett_4i4_USB-00.pro-output-0</t>
+  </si>
+  <si>
+    <t>2026-10-18T19:20:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-18T20:25:00+02:00</t>
+  </si>
+  <si>
+    <t>1h05m</t>
+  </si>
+  <si>
+    <t>mpd</t>
+  </si>
+  <si>
+    <t>The Disintegration Loops I</t>
+  </si>
+  <si>
+    <t>William Basinski</t>
+  </si>
+  <si>
+    <t>sync/basinski/dlp1.flac</t>
+  </si>
+  <si>
+    <t>2026-10-19T20:30:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T21:40:00+02:00</t>
   </si>
   <si>
     <t>1h10m</t>
   </si>
   <si>
-    <t>mpd</t>
-  </si>
-  <si>
-    <t>Selected Ambient Works Volume II</t>
-  </si>
-  <si>
-    <t>Aphex Twin</t>
-  </si>
-  <si>
-    <t>sync/afx/saw2-03.flac</t>
-  </si>
-  <si>
-    <t>alsa_output.usb-Focusrite_Scarlett_4i4_USB-00.pro-output-0</t>
-  </si>
-  <si>
-    <t>2026-10-18T22:00:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-18T23:10:00+02:00</t>
-  </si>
-  <si>
-    <t>The Disintegration Loops I</t>
-  </si>
-  <si>
-    <t>William Basinski</t>
-  </si>
-  <si>
-    <t>sync/basinski/dlp1.flac</t>
-  </si>
-  <si>
-    <t>2026-10-18T23:37:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-18T23:47:00+02:00</t>
-  </si>
-  <si>
-    <t>10m00s</t>
-  </si>
-  <si>
-    <t>Harmony of Difference</t>
-  </si>
-  <si>
-    <t>Kamasi Washington</t>
-  </si>
-  <si>
-    <t>sync/kamasi/truth.flac</t>
-  </si>
-  <si>
-    <t>2026-10-19T21:25:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-19T23:35:00+02:00</t>
-  </si>
-  <si>
-    <t>2h10m</t>
-  </si>
-  <si>
     <t>Discreet Music</t>
   </si>
   <si>
@@ -137,16 +125,34 @@
     <t>sync/eno/discreet.flac</t>
   </si>
   <si>
-    <t>1h35m</t>
-  </si>
-  <si>
-    <t>2026-10-20T22:30:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-20T23:30:00+02:00</t>
-  </si>
-  <si>
-    <t>1h00m</t>
+    <t>2026-10-19T21:51:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:46:00+02:00</t>
+  </si>
+  <si>
+    <t>55m00s</t>
+  </si>
+  <si>
+    <t>A Rainbow in Curved Air</t>
+  </si>
+  <si>
+    <t>Terry Riley</t>
+  </si>
+  <si>
+    <t>sync/riley/rainbow.flac</t>
+  </si>
+  <si>
+    <t>46m00s</t>
+  </si>
+  <si>
+    <t>2026-10-20T21:45:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-20T23:50:00+02:00</t>
+  </si>
+  <si>
+    <t>2h05m</t>
   </si>
   <si>
     <t>Symphony No. 3, Op. 36: II. Lento</t>
@@ -158,6 +164,9 @@
     <t>sync/gorecki/02.flac</t>
   </si>
   <si>
+    <t>1h50m</t>
+  </si>
+  <si>
     <t>Hosts</t>
   </si>
   <si>
@@ -179,10 +188,10 @@
     <t>Chain</t>
   </si>
   <si>
-    <t>intact (5069 lines)</t>
-  </si>
-  <si>
-    <t>ce2 2026-10-18 … 2026-10-20  (3 days)</t>
+    <t>intact (5067 lines)</t>
+  </si>
+  <si>
+    <t>ce2 2026-10-18 … 2026-10-21  (4 days)</t>
   </si>
   <si>
     <t>dfn not yet stamped, digicert not yet stamped</t>
@@ -628,16 +637,16 @@
         <v>22</v>
       </c>
       <c r="J2">
-        <v>0.37</v>
+        <v>0.317</v>
       </c>
       <c r="K2">
-        <v>0.405</v>
+        <v>0.34</v>
       </c>
       <c r="L2">
-        <v>0.43</v>
+        <v>0.35</v>
       </c>
       <c r="M2">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -651,37 +660,34 @@
         <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
       </c>
       <c r="J3">
-        <v>0.39</v>
+        <v>0.431</v>
       </c>
       <c r="K3">
-        <v>0.426</v>
+        <v>0.46</v>
       </c>
       <c r="L3">
-        <v>0.45</v>
+        <v>0.489</v>
       </c>
       <c r="M3">
-        <v>16</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -689,43 +695,40 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I4" t="s">
         <v>22</v>
       </c>
       <c r="J4">
-        <v>0.421</v>
+        <v>0.38</v>
       </c>
       <c r="K4">
+        <v>0.416</v>
+      </c>
+      <c r="L4">
         <v>0.44</v>
       </c>
-      <c r="L4">
-        <v>0.468</v>
-      </c>
       <c r="M4">
-        <v>4</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -733,43 +736,43 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I5" t="s">
         <v>22</v>
       </c>
       <c r="J5">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="K5">
-        <v>0.5045</v>
+        <v>0.432</v>
       </c>
       <c r="L5">
-        <v>0.596</v>
+        <v>0.459</v>
       </c>
       <c r="M5">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -777,43 +780,43 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I6" t="s">
         <v>22</v>
       </c>
       <c r="J6">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="K6">
-        <v>0.3945</v>
+        <v>0.554</v>
       </c>
       <c r="L6">
-        <v>0.43</v>
+        <v>0.7</v>
       </c>
       <c r="M6">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -832,50 +835,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/examples/report.xlsx
+++ b/examples/report.xlsx
@@ -125,13 +125,13 @@
     <t>sync/eno/discreet.flac</t>
   </si>
   <si>
-    <t>2026-10-19T21:51:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-19T22:46:00+02:00</t>
-  </si>
-  <si>
-    <t>55m00s</t>
+    <t>2026-10-19T21:55:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:45:00+02:00</t>
+  </si>
+  <si>
+    <t>50m00s</t>
   </si>
   <si>
     <t>A Rainbow in Curved Air</t>
@@ -143,7 +143,7 @@
     <t>sync/riley/rainbow.flac</t>
   </si>
   <si>
-    <t>46m00s</t>
+    <t>45m00s</t>
   </si>
   <si>
     <t>2026-10-20T21:45:00+02:00</t>
@@ -188,7 +188,7 @@
     <t>Chain</t>
   </si>
   <si>
-    <t>intact (5067 lines)</t>
+    <t>intact (4720 lines)</t>
   </si>
   <si>
     <t>ce2 2026-10-18 … 2026-10-21  (4 days)</t>
@@ -197,7 +197,7 @@
     <t>dfn not yet stamped, digicert not yet stamped</t>
   </si>
   <si>
-    <t>ce3 2026-10-21</t>
+    <t>ce3 2026-10-18 … 2026-10-21  (4 days)</t>
   </si>
 </sst>
 </file>
@@ -763,13 +763,13 @@
         <v>0.4</v>
       </c>
       <c r="K5">
-        <v>0.432</v>
+        <v>0.44</v>
       </c>
       <c r="L5">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="M5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>42</v>

--- a/examples/report.xlsx
+++ b/examples/report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="111">
   <si>
     <t>Host</t>
   </si>
@@ -65,10 +65,10 @@
     <t>2026-10-18T14:40:00+02:00</t>
   </si>
   <si>
-    <t>2026-10-18T16:40:00+02:00</t>
-  </si>
-  <si>
-    <t>2h00m</t>
+    <t>2026-10-18T16:44:00+02:00</t>
+  </si>
+  <si>
+    <t>2h04m</t>
   </si>
   <si>
     <t>mpv</t>
@@ -89,82 +89,232 @@
     <t>2026-10-18T19:20:00+02:00</t>
   </si>
   <si>
-    <t>2026-10-18T20:25:00+02:00</t>
-  </si>
-  <si>
-    <t>1h05m</t>
+    <t>2026-10-18T19:50:00+02:00</t>
+  </si>
+  <si>
+    <t>30m00s</t>
   </si>
   <si>
     <t>mpd</t>
   </si>
   <si>
-    <t>The Disintegration Loops I</t>
+    <t>Discreet Music</t>
+  </si>
+  <si>
+    <t>Brian Eno</t>
+  </si>
+  <si>
+    <t>sync/eno/01.flac</t>
+  </si>
+  <si>
+    <t>2026-10-18T19:51:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-18T19:59:00+02:00</t>
+  </si>
+  <si>
+    <t>8m00s</t>
+  </si>
+  <si>
+    <t>Fullness of Wind</t>
+  </si>
+  <si>
+    <t>sync/eno/02.flac</t>
+  </si>
+  <si>
+    <t>2026-10-18T20:00:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-18T20:04:00+02:00</t>
+  </si>
+  <si>
+    <t>4m00s</t>
+  </si>
+  <si>
+    <t>French Catalogues</t>
+  </si>
+  <si>
+    <t>sync/eno/03.flac</t>
+  </si>
+  <si>
+    <t>2026-10-18T20:05:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-18T20:11:00+02:00</t>
+  </si>
+  <si>
+    <t>6m00s</t>
+  </si>
+  <si>
+    <t>Brutal Ardour</t>
+  </si>
+  <si>
+    <t>sync/eno/04.flac</t>
+  </si>
+  <si>
+    <t>2026-10-18T20:12:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-18T20:26:00+02:00</t>
+  </si>
+  <si>
+    <t>14m00s</t>
+  </si>
+  <si>
+    <t>2026-10-19T20:30:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T21:32:00+02:00</t>
+  </si>
+  <si>
+    <t>1h02m</t>
+  </si>
+  <si>
+    <t>dlp 1.1</t>
   </si>
   <si>
     <t>William Basinski</t>
   </si>
   <si>
-    <t>sync/basinski/dlp1.flac</t>
-  </si>
-  <si>
-    <t>2026-10-19T20:30:00+02:00</t>
-  </si>
-  <si>
-    <t>2026-10-19T21:40:00+02:00</t>
-  </si>
-  <si>
-    <t>1h10m</t>
-  </si>
-  <si>
-    <t>Discreet Music</t>
-  </si>
-  <si>
-    <t>Brian Eno</t>
-  </si>
-  <si>
-    <t>sync/eno/discreet.flac</t>
+    <t>sync/basinski/01.flac</t>
+  </si>
+  <si>
+    <t>2026-10-19T21:36:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T21:42:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T21:51:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T21:54:00+02:00</t>
+  </si>
+  <si>
+    <t>3m00s</t>
+  </si>
+  <si>
+    <t>Knowledge</t>
+  </si>
+  <si>
+    <t>Kamasi Washington</t>
+  </si>
+  <si>
+    <t>sync/kamasi/03.flac</t>
   </si>
   <si>
     <t>2026-10-19T21:55:00+02:00</t>
   </si>
   <si>
-    <t>2026-10-19T22:45:00+02:00</t>
-  </si>
-  <si>
-    <t>50m00s</t>
-  </si>
-  <si>
-    <t>A Rainbow in Curved Air</t>
-  </si>
-  <si>
-    <t>Terry Riley</t>
-  </si>
-  <si>
-    <t>sync/riley/rainbow.flac</t>
-  </si>
-  <si>
-    <t>45m00s</t>
+    <t>2026-10-19T21:58:00+02:00</t>
+  </si>
+  <si>
+    <t>Perspective</t>
+  </si>
+  <si>
+    <t>sync/kamasi/04.flac</t>
+  </si>
+  <si>
+    <t>2026-10-19T21:59:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:03:00+02:00</t>
+  </si>
+  <si>
+    <t>Integrity</t>
+  </si>
+  <si>
+    <t>sync/kamasi/05.flac</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:04:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:16:00+02:00</t>
+  </si>
+  <si>
+    <t>12m00s</t>
+  </si>
+  <si>
+    <t>Truth</t>
+  </si>
+  <si>
+    <t>sync/kamasi/06.flac</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:17:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:20:00+02:00</t>
+  </si>
+  <si>
+    <t>Desire</t>
+  </si>
+  <si>
+    <t>sync/kamasi/01.flac</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:24:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:27:00+02:00</t>
+  </si>
+  <si>
+    <t>Humility</t>
+  </si>
+  <si>
+    <t>sync/kamasi/02.flac</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:28:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:31:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:32:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:35:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:36:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:40:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:41:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:53:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:54:00+02:00</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:56:00+02:00</t>
+  </si>
+  <si>
+    <t>2m00s</t>
   </si>
   <si>
     <t>2026-10-20T21:45:00+02:00</t>
   </si>
   <si>
-    <t>2026-10-20T23:50:00+02:00</t>
-  </si>
-  <si>
-    <t>2h05m</t>
-  </si>
-  <si>
-    <t>Symphony No. 3, Op. 36: II. Lento</t>
-  </si>
-  <si>
-    <t>Henryk Górecki</t>
-  </si>
-  <si>
-    <t>sync/gorecki/02.flac</t>
-  </si>
-  <si>
-    <t>1h50m</t>
+    <t>2026-10-20T23:49:00+02:00</t>
+  </si>
+  <si>
+    <t>II (Continuous Mix)</t>
+  </si>
+  <si>
+    <t>Voices from the Lake</t>
+  </si>
+  <si>
+    <t>sync/vftl/01.flac</t>
+  </si>
+  <si>
+    <t>1h49m</t>
   </si>
   <si>
     <t>Hosts</t>
@@ -188,7 +338,7 @@
     <t>Chain</t>
   </si>
   <si>
-    <t>intact (4720 lines)</t>
+    <t>intact (6853 lines)</t>
   </si>
   <si>
     <t>ce2 2026-10-18 … 2026-10-21  (4 days)</t>
@@ -547,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -640,13 +790,13 @@
         <v>0.317</v>
       </c>
       <c r="K2">
-        <v>0.34</v>
+        <v>0.341</v>
       </c>
       <c r="L2">
         <v>0.35</v>
       </c>
       <c r="M2">
-        <v>26</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -678,16 +828,16 @@
         <v>22</v>
       </c>
       <c r="J3">
-        <v>0.431</v>
+        <v>0.46</v>
       </c>
       <c r="K3">
-        <v>0.46</v>
+        <v>0.483</v>
       </c>
       <c r="L3">
         <v>0.489</v>
       </c>
       <c r="M3">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -710,25 +860,25 @@
         <v>33</v>
       </c>
       <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
         <v>34</v>
       </c>
-      <c r="H4" t="s">
-        <v>35</v>
-      </c>
       <c r="I4" t="s">
         <v>22</v>
       </c>
       <c r="J4">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
       <c r="K4">
-        <v>0.416</v>
+        <v>0.4665</v>
       </c>
       <c r="L4">
-        <v>0.44</v>
+        <v>0.473</v>
       </c>
       <c r="M4">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -736,43 +886,40 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
         <v>36</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>37</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
         <v>38</v>
       </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
         <v>39</v>
       </c>
-      <c r="G5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" t="s">
-        <v>41</v>
-      </c>
       <c r="I5" t="s">
         <v>22</v>
       </c>
       <c r="J5">
-        <v>0.4</v>
+        <v>0.447</v>
       </c>
       <c r="K5">
-        <v>0.44</v>
+        <v>0.447</v>
       </c>
       <c r="L5">
-        <v>0.46</v>
+        <v>0.447</v>
       </c>
       <c r="M5">
-        <v>11</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -780,43 +927,685 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
         <v>43</v>
       </c>
-      <c r="C6" t="s">
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
         <v>44</v>
       </c>
-      <c r="D6" t="s">
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6">
+        <v>0.431</v>
+      </c>
+      <c r="K6">
+        <v>0.437</v>
+      </c>
+      <c r="L6">
+        <v>0.437</v>
+      </c>
+      <c r="M6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
         <v>45</v>
       </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="C7" t="s">
         <v>46</v>
       </c>
-      <c r="G6" t="s">
+      <c r="D7" t="s">
         <v>47</v>
       </c>
-      <c r="H6" t="s">
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7">
+        <v>0.431</v>
+      </c>
+      <c r="K7">
+        <v>0.431</v>
+      </c>
+      <c r="L7">
+        <v>0.447</v>
+      </c>
+      <c r="M7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
         <v>48</v>
       </c>
-      <c r="I6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6">
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8">
+        <v>0.385</v>
+      </c>
+      <c r="K8">
+        <v>0.422</v>
+      </c>
+      <c r="L8">
+        <v>0.44</v>
+      </c>
+      <c r="M8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9">
+        <v>0.38</v>
+      </c>
+      <c r="K9">
+        <v>0.381</v>
+      </c>
+      <c r="L9">
+        <v>0.381</v>
+      </c>
+      <c r="M9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10">
+        <v>0.43</v>
+      </c>
+      <c r="K10">
+        <v>0.43</v>
+      </c>
+      <c r="L10">
+        <v>0.43</v>
+      </c>
+      <c r="M10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11">
+        <v>0.439</v>
+      </c>
+      <c r="K11">
+        <v>0.439</v>
+      </c>
+      <c r="L11">
+        <v>0.439</v>
+      </c>
+      <c r="M11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12">
+        <v>0.439</v>
+      </c>
+      <c r="K12">
+        <v>0.449</v>
+      </c>
+      <c r="L12">
+        <v>0.449</v>
+      </c>
+      <c r="M12">
+        <v>6</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13">
+        <v>0.449</v>
+      </c>
+      <c r="K13">
+        <v>0.4575</v>
+      </c>
+      <c r="L13">
+        <v>0.46</v>
+      </c>
+      <c r="M13">
+        <v>14</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14">
+        <v>0.454</v>
+      </c>
+      <c r="K14">
+        <v>0.459</v>
+      </c>
+      <c r="L14">
+        <v>0.459</v>
+      </c>
+      <c r="M14">
+        <v>5</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" t="s">
+        <v>82</v>
+      </c>
+      <c r="I15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15">
+        <v>0.446</v>
+      </c>
+      <c r="K15">
+        <v>0.446</v>
+      </c>
+      <c r="L15">
+        <v>0.454</v>
+      </c>
+      <c r="M15">
+        <v>5</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" t="s">
+        <v>61</v>
+      </c>
+      <c r="I16" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16">
+        <v>0.436</v>
+      </c>
+      <c r="K16">
+        <v>0.446</v>
+      </c>
+      <c r="L16">
+        <v>0.446</v>
+      </c>
+      <c r="M16">
+        <v>5</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17">
+        <v>0.424</v>
+      </c>
+      <c r="K17">
+        <v>0.436</v>
+      </c>
+      <c r="L17">
+        <v>0.436</v>
+      </c>
+      <c r="M17">
+        <v>5</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18">
+        <v>0.414</v>
+      </c>
+      <c r="K18">
+        <v>0.424</v>
+      </c>
+      <c r="L18">
+        <v>0.424</v>
+      </c>
+      <c r="M18">
+        <v>6</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19" t="s">
+        <v>74</v>
+      </c>
+      <c r="I19" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19">
+        <v>0.401</v>
+      </c>
+      <c r="K19">
+        <v>0.406</v>
+      </c>
+      <c r="L19">
+        <v>0.414</v>
+      </c>
+      <c r="M19">
+        <v>14</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" t="s">
+        <v>78</v>
+      </c>
+      <c r="I20" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20">
+        <v>0.4</v>
+      </c>
+      <c r="K20">
+        <v>0.4005</v>
+      </c>
+      <c r="L20">
+        <v>0.401</v>
+      </c>
+      <c r="M20">
+        <v>4</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" t="s">
+        <v>97</v>
+      </c>
+      <c r="H21" t="s">
+        <v>98</v>
+      </c>
+      <c r="I21" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21">
         <v>0.42</v>
       </c>
-      <c r="K6">
+      <c r="K21">
         <v>0.554</v>
       </c>
-      <c r="L6">
-        <v>0.7</v>
-      </c>
-      <c r="M6">
-        <v>27</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>49</v>
+      <c r="L21">
+        <v>0.689</v>
+      </c>
+      <c r="M21">
+        <v>127</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -835,50 +1624,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/examples/report.xlsx
+++ b/examples/report.xlsx
@@ -787,13 +787,13 @@
         <v>22</v>
       </c>
       <c r="J2">
-        <v>0.317</v>
+        <v>0.681846194135301</v>
       </c>
       <c r="K2">
-        <v>0.341</v>
+        <v>0.6986368027818106</v>
       </c>
       <c r="L2">
-        <v>0.35</v>
+        <v>0.7047298732064892</v>
       </c>
       <c r="M2">
         <v>126</v>
@@ -828,13 +828,13 @@
         <v>22</v>
       </c>
       <c r="J3">
-        <v>0.46</v>
+        <v>0.7719442629361641</v>
       </c>
       <c r="K3">
-        <v>0.483</v>
+        <v>0.7846013365124446</v>
       </c>
       <c r="L3">
-        <v>0.489</v>
+        <v>0.7878368425460937</v>
       </c>
       <c r="M3">
         <v>32</v>
@@ -869,13 +869,13 @@
         <v>22</v>
       </c>
       <c r="J4">
-        <v>0.46</v>
+        <v>0.7719442629361641</v>
       </c>
       <c r="K4">
-        <v>0.4665</v>
+        <v>0.7755632395372396</v>
       </c>
       <c r="L4">
-        <v>0.473</v>
+        <v>0.7791487535639231</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -910,13 +910,13 @@
         <v>22</v>
       </c>
       <c r="J5">
-        <v>0.447</v>
+        <v>0.7646027242213619</v>
       </c>
       <c r="K5">
-        <v>0.447</v>
+        <v>0.7646027242213619</v>
       </c>
       <c r="L5">
-        <v>0.447</v>
+        <v>0.7646027242213619</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -951,13 +951,13 @@
         <v>22</v>
       </c>
       <c r="J6">
-        <v>0.431</v>
+        <v>0.755368882500193</v>
       </c>
       <c r="K6">
-        <v>0.437</v>
+        <v>0.7588579337781816</v>
       </c>
       <c r="L6">
-        <v>0.437</v>
+        <v>0.7588579337781816</v>
       </c>
       <c r="M6">
         <v>8</v>
@@ -992,13 +992,13 @@
         <v>22</v>
       </c>
       <c r="J7">
-        <v>0.431</v>
+        <v>0.755368882500193</v>
       </c>
       <c r="K7">
-        <v>0.431</v>
+        <v>0.755368882500193</v>
       </c>
       <c r="L7">
-        <v>0.447</v>
+        <v>0.7646027242213619</v>
       </c>
       <c r="M7">
         <v>16</v>
@@ -1033,13 +1033,13 @@
         <v>22</v>
       </c>
       <c r="J8">
-        <v>0.385</v>
+        <v>0.7274786348791457</v>
       </c>
       <c r="K8">
-        <v>0.422</v>
+        <v>0.7500740667593202</v>
       </c>
       <c r="L8">
-        <v>0.44</v>
+        <v>0.7605904921522784</v>
       </c>
       <c r="M8">
         <v>64</v>
@@ -1074,13 +1074,13 @@
         <v>22</v>
       </c>
       <c r="J9">
-        <v>0.38</v>
+        <v>0.7243156443441741</v>
       </c>
       <c r="K9">
-        <v>0.381</v>
+        <v>0.7249504524205013</v>
       </c>
       <c r="L9">
-        <v>0.381</v>
+        <v>0.7249504524205013</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -1115,13 +1115,13 @@
         <v>22</v>
       </c>
       <c r="J10">
-        <v>0.43</v>
+        <v>0.7547842314287575</v>
       </c>
       <c r="K10">
-        <v>0.43</v>
+        <v>0.7547842314287575</v>
       </c>
       <c r="L10">
-        <v>0.43</v>
+        <v>0.7547842314287575</v>
       </c>
       <c r="M10">
         <v>5</v>
@@ -1156,13 +1156,13 @@
         <v>22</v>
       </c>
       <c r="J11">
-        <v>0.439</v>
+        <v>0.760013850163107</v>
       </c>
       <c r="K11">
-        <v>0.439</v>
+        <v>0.760013850163107</v>
       </c>
       <c r="L11">
-        <v>0.439</v>
+        <v>0.760013850163107</v>
       </c>
       <c r="M11">
         <v>5</v>
@@ -1197,13 +1197,13 @@
         <v>22</v>
       </c>
       <c r="J12">
-        <v>0.439</v>
+        <v>0.760013850163107</v>
       </c>
       <c r="K12">
-        <v>0.449</v>
+        <v>0.7657413747855265</v>
       </c>
       <c r="L12">
-        <v>0.449</v>
+        <v>0.7657413747855265</v>
       </c>
       <c r="M12">
         <v>6</v>
@@ -1241,13 +1241,13 @@
         <v>22</v>
       </c>
       <c r="J13">
-        <v>0.449</v>
+        <v>0.7657413747855265</v>
       </c>
       <c r="K13">
-        <v>0.4575</v>
+        <v>0.770543272083954</v>
       </c>
       <c r="L13">
-        <v>0.46</v>
+        <v>0.7719442629361641</v>
       </c>
       <c r="M13">
         <v>14</v>
@@ -1285,13 +1285,13 @@
         <v>22</v>
       </c>
       <c r="J14">
-        <v>0.454</v>
+        <v>0.7685732843416645</v>
       </c>
       <c r="K14">
-        <v>0.459</v>
+        <v>0.7713844771974706</v>
       </c>
       <c r="L14">
-        <v>0.459</v>
+        <v>0.7713844771974706</v>
       </c>
       <c r="M14">
         <v>5</v>
@@ -1329,13 +1329,13 @@
         <v>22</v>
       </c>
       <c r="J15">
-        <v>0.446</v>
+        <v>0.7640321249615055</v>
       </c>
       <c r="K15">
-        <v>0.446</v>
+        <v>0.7640321249615055</v>
       </c>
       <c r="L15">
-        <v>0.454</v>
+        <v>0.7685732843416645</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -1373,13 +1373,13 @@
         <v>22</v>
       </c>
       <c r="J16">
-        <v>0.436</v>
+        <v>0.7582786526875782</v>
       </c>
       <c r="K16">
-        <v>0.446</v>
+        <v>0.7640321249615055</v>
       </c>
       <c r="L16">
-        <v>0.446</v>
+        <v>0.7640321249615055</v>
       </c>
       <c r="M16">
         <v>5</v>
@@ -1417,13 +1417,13 @@
         <v>22</v>
       </c>
       <c r="J17">
-        <v>0.424</v>
+        <v>0.7512571508442144</v>
       </c>
       <c r="K17">
-        <v>0.436</v>
+        <v>0.7582786526875782</v>
       </c>
       <c r="L17">
-        <v>0.436</v>
+        <v>0.7582786526875782</v>
       </c>
       <c r="M17">
         <v>5</v>
@@ -1461,13 +1461,13 @@
         <v>22</v>
       </c>
       <c r="J18">
-        <v>0.414</v>
+        <v>0.7453039913720836</v>
       </c>
       <c r="K18">
-        <v>0.424</v>
+        <v>0.7512571508442144</v>
       </c>
       <c r="L18">
-        <v>0.424</v>
+        <v>0.7512571508442144</v>
       </c>
       <c r="M18">
         <v>6</v>
@@ -1505,13 +1505,13 @@
         <v>22</v>
       </c>
       <c r="J19">
-        <v>0.401</v>
+        <v>0.7374197940162812</v>
       </c>
       <c r="K19">
-        <v>0.406</v>
+        <v>0.7404720630522144</v>
       </c>
       <c r="L19">
-        <v>0.414</v>
+        <v>0.7453039913720836</v>
       </c>
       <c r="M19">
         <v>14</v>
@@ -1549,13 +1549,13 @@
         <v>22</v>
       </c>
       <c r="J20">
-        <v>0.4</v>
+        <v>0.7368062997280773</v>
       </c>
       <c r="K20">
-        <v>0.4005</v>
+        <v>0.7371131745239615</v>
       </c>
       <c r="L20">
-        <v>0.401</v>
+        <v>0.7374197940162812</v>
       </c>
       <c r="M20">
         <v>4</v>
@@ -1593,13 +1593,13 @@
         <v>22</v>
       </c>
       <c r="J21">
-        <v>0.42</v>
+        <v>0.7488872387218507</v>
       </c>
       <c r="K21">
-        <v>0.554</v>
+        <v>0.8213027082338559</v>
       </c>
       <c r="L21">
-        <v>0.689</v>
+        <v>0.8832284990891334</v>
       </c>
       <c r="M21">
         <v>127</v>

--- a/examples/report.xlsx
+++ b/examples/report.xlsx
@@ -44,13 +44,13 @@
     <t>Output</t>
   </si>
   <si>
-    <t>Gain min</t>
-  </si>
-  <si>
-    <t>Gain median</t>
-  </si>
-  <si>
-    <t>Gain max</t>
+    <t>Volume min</t>
+  </si>
+  <si>
+    <t>Volume median</t>
+  </si>
+  <si>
+    <t>Volume max</t>
   </si>
   <si>
     <t>Samples</t>

--- a/examples/report.xlsx
+++ b/examples/report.xlsx
@@ -341,13 +341,13 @@
     <t>intact (6853 lines)</t>
   </si>
   <si>
-    <t>ce2 2026-10-18 … 2026-10-21  (4 days)</t>
+    <t>ce2 18-10-2026 … 21-10-2026  (4 days)</t>
   </si>
   <si>
     <t>dfn not yet stamped, digicert not yet stamped</t>
   </si>
   <si>
-    <t>ce3 2026-10-18 … 2026-10-21  (4 days)</t>
+    <t>ce3 18-10-2026 … 21-10-2026  (4 days)</t>
   </si>
 </sst>
 </file>

--- a/examples/report.xlsx
+++ b/examples/report.xlsx
@@ -338,7 +338,7 @@
     <t>Chain</t>
   </si>
   <si>
-    <t>intact (6853 lines)</t>
+    <t>intact (6572 lines)</t>
   </si>
   <si>
     <t>ce2 18-10-2026 … 21-10-2026  (4 days)</t>

--- a/examples/report.xlsx
+++ b/examples/report.xlsx
@@ -344,7 +344,7 @@
     <t>ce2 18-10-2026 … 21-10-2026  (4 days)</t>
   </si>
   <si>
-    <t>dfn not yet stamped, digicert not yet stamped</t>
+    <t>dfn not yet stamped, digicert not yet stamped — the oldest for 5 days</t>
   </si>
   <si>
     <t>ce3 18-10-2026 … 21-10-2026  (4 days)</t>
